--- a/extenbooks/S1103_extenbook.xlsx
+++ b/extenbooks/S1103_extenbook.xlsx
@@ -3604,7 +3604,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -4817,11 +4817,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4844,76 +4844,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LOP at Aggregate Level US/Japan (Fig 11.6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1103_research.json", "adequacy_report": "Technical/docs/chapters/CH11_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1103_DPR.md", "epr": "Technical/docs/series/S1103_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1103_load.py", "processor": "Technical/code/P02_processors/P02_S1103_construct.py", "validator": "Technical/code/V03_validators/V03_S1103_validate.py", "processed": "Technical/data/processed/S1103.parquet", "chopped_csv": "Technical/chopped/S1103.csv"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:56:16.880881+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1103_extenbook.xlsx
+++ b/extenbooks/S1103_extenbook.xlsx
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-18T23:11:36.756266+00:00</t>
+          <t>2026-07-02T06:18:42.042112+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1103_extenbook.xlsx
+++ b/extenbooks/S1103_extenbook.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02T06:18:42.042112+00:00</t>
+          <t>2026-07-11T03:44:22.494331+00:00</t>
         </is>
       </c>
     </row>
@@ -4817,11 +4817,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4844,6 +4844,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BLS_ILC_LOP_RATIO_APPENDIX_11_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful reconstruction of Figure 11.6 (aggregate LOP test, real exchange rate over adjusted unit labor costs) from BLS data; figure reference verified correct (11.6).", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1103_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1103_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 11.6; formula construction. Phase 9 extension requires both numerator and denominator re-derivation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ratio_dimensionless</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
